--- a/template/7.11/净值.xlsx
+++ b/template/7.11/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3350,18 +3350,294 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="0" t="n">
         <v>0.99807</v>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="0" t="inlineStr">
         <is>
           <t>-0.1969%</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="0" t="n">
         <v>0.9932800000000001</v>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B102" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D105" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E105" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B106" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E108" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B109" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D109" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B112" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E113" t="inlineStr">
         <is>
           <t>-0.6759%</t>
         </is>
@@ -3379,7 +3655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -5696,18 +5972,294 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="0" t="n">
         <v>0.99661</v>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="0" t="inlineStr">
         <is>
           <t>-0.3427%</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="0" t="n">
         <v>0.99182</v>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B102" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D105" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E105" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B106" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E108" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B109" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D109" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B112" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E113" t="inlineStr">
         <is>
           <t>-0.8216%</t>
         </is>
@@ -5725,7 +6277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -7653,18 +8205,294 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="0" t="n">
         <v>0.98321</v>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="0" t="inlineStr">
         <is>
           <t>-3.9918%</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="0" t="n">
         <v>0.9825</v>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B86" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D89" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D90" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D91" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B92" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D92" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E92" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B93" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D93" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D94" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>-4.0399%</t>
         </is>
@@ -7681,7 +8509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -9609,18 +10437,294 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="0" t="n">
         <v>1.00315</v>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="0" t="inlineStr">
         <is>
           <t>-2.4484%</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="0" t="n">
         <v>1.00244</v>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B86" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D89" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D90" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D91" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B92" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D92" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E92" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B93" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D93" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D94" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>-2.496%</t>
         </is>
@@ -9638,7 +10742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -10324,18 +11428,294 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="0" t="n">
         <v>0.99372</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>-0.707%</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="0" t="n">
         <v>0.99166</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>-0.9021%</t>
         </is>
@@ -10352,7 +11732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -11038,18 +12418,294 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="0" t="n">
         <v>1.00007</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>-0.0733%</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="0" t="n">
         <v>0.998</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>-0.2683%</t>
         </is>

--- a/template/7.11/净值.xlsx
+++ b/template/7.11/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3626,18 +3626,317 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="0" t="n">
         <v>0.99807</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="0" t="inlineStr">
         <is>
           <t>-0.1969%</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="0" t="n">
         <v>0.9932800000000001</v>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B117" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B118" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E118" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B119" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B120" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B121" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B122" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B123" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B124" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E124" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B125" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E125" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E126" t="inlineStr">
         <is>
           <t>-0.6759%</t>
         </is>
@@ -3655,7 +3954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -6248,18 +6547,317 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="0" t="n">
         <v>0.99661</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="0" t="inlineStr">
         <is>
           <t>-0.3427%</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="0" t="n">
         <v>0.99182</v>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B117" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B118" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E118" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B119" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E119" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B120" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E120" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B121" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E121" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B122" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B123" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B124" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E124" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B125" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E125" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E126" t="inlineStr">
         <is>
           <t>-0.8216%</t>
         </is>
@@ -6277,7 +6875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -8481,18 +9079,317 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="0" t="n">
         <v>0.98321</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="0" t="inlineStr">
         <is>
           <t>-3.9918%</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>0.9825</v>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B102" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D105" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E105" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B106" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E108" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>-4.0399%</t>
         </is>
@@ -8509,7 +9406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -10713,18 +11610,317 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="0" t="n">
         <v>1.00315</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="0" t="inlineStr">
         <is>
           <t>-2.4484%</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>1.00244</v>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B102" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D105" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E105" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B106" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E108" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>-2.496%</t>
         </is>
@@ -10742,7 +11938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -11704,18 +12900,317 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>0.99372</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>-0.707%</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.99166</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>-0.9021%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.99372</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>-0.707%</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.99166</v>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>-0.9021%</t>
         </is>
@@ -11732,7 +13227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -12694,18 +14189,317 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>1.00007</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>-0.0733%</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.998</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>-0.2683%</t>
         </is>

--- a/template/7.11/净值.xlsx
+++ b/template/7.11/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3925,18 +3925,87 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="0" t="n">
         <v>0.99807</v>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="0" t="inlineStr">
         <is>
           <t>-0.1969%</t>
         </is>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="0" t="n">
         <v>0.9932800000000001</v>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B127" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D127" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t>-0.6759%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.99807</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>-0.1969%</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0.9932800000000001</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>-0.6759%</t>
         </is>
@@ -3954,7 +4023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -6846,18 +6915,87 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="0" t="n">
         <v>0.99661</v>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="0" t="inlineStr">
         <is>
           <t>-0.3427%</t>
         </is>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="0" t="n">
         <v>0.99182</v>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B127" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D127" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.99661</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>-0.3427%</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>-0.8216%</t>
         </is>
@@ -6875,7 +7013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -9378,18 +9516,87 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="0" t="n">
         <v>0.98321</v>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="0" t="inlineStr">
         <is>
           <t>-3.9918%</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="0" t="n">
         <v>0.9825</v>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>-4.0399%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.98321</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>-3.9918%</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="E112" t="inlineStr">
         <is>
           <t>-4.0399%</t>
         </is>
@@ -9406,7 +9613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -11909,18 +12116,87 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="0" t="n">
         <v>1.00315</v>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="0" t="inlineStr">
         <is>
           <t>-2.4484%</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="0" t="n">
         <v>1.00244</v>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>2025/07/11</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E112" t="inlineStr">
         <is>
           <t>-2.496%</t>
         </is>
@@ -13199,18 +13475,18 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="0" t="n">
         <v>0.99372</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>-0.707%</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="0" t="n">
         <v>0.99166</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="0" t="inlineStr">
         <is>
           <t>-0.9021%</t>
         </is>
@@ -14488,18 +14764,18 @@
           <t>2025/07/11</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="0" t="n">
         <v>1.00007</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>-0.0733%</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="0" t="n">
         <v>0.998</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="0" t="inlineStr">
         <is>
           <t>-0.2683%</t>
         </is>
